--- a/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>ORGO</t>
   </si>
@@ -656,96 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>433100</v>
+      </c>
+      <c r="E8" s="3">
         <v>450900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>468100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>338300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>261000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>193400</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
@@ -753,30 +756,33 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E9" s="3">
         <v>105000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>114200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>75900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>68800</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,30 +798,33 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>326700</v>
+      </c>
+      <c r="E10" s="3">
         <v>345900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>353900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>251000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>185000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>124600</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,29 +861,30 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E12" s="3">
         <v>39800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10700</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,9 +942,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -936,20 +955,20 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -965,9 +984,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,37 +1044,38 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>420600</v>
+      </c>
+      <c r="E17" s="3">
         <v>428600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>397000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>309400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>292700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>247100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
@@ -1057,38 +1083,41 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E18" s="3">
         <v>22300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>71000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-53700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,37 +1146,38 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1152,30 +1185,33 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E21" s="3">
         <v>33000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-46900</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,30 +1227,33 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10900</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,38 +1269,41 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>20300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>63800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-38600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-64700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1269,38 +1311,41 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E24" s="3">
         <v>4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-31100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,38 +1395,41 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>15500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>94900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-64800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1386,38 +1437,41 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E27" s="3">
         <v>15500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>94900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-64800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,38 +1647,41 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1620,38 +1689,41 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E33" s="3">
         <v>15500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>94900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-64800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="L33" s="3">
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,38 +1773,41 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E35" s="3">
         <v>15500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>94900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-64800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="L35" s="3">
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
@@ -1737,53 +1815,59 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,47 +1901,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E41" s="3">
         <v>102500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>113900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>84400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1893,30 +1982,33 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E43" s="3">
         <v>89500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>56800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>39400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,30 +2024,33 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E44" s="3">
         <v>24800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1971,36 +2066,39 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2010,48 +2108,54 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E46" s="3">
         <v>222600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>227000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>174300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>125600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>71100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2061,18 +2165,18 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2088,30 +2192,33 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E48" s="3">
         <v>145700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>128300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>60100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,30 +2234,33 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E49" s="3">
         <v>49600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>54400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>59400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>46300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>51600</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,48 +2360,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E52" s="3">
         <v>31500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>33500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>312500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>310000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E54" s="3">
         <v>449400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>443300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>294500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>220700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>163700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>312800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>311400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,29 +2525,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E57" s="3">
         <v>32300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,147 +2564,159 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E59" s="3">
         <v>38200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>37200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E60" s="3">
         <v>75000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>68200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E61" s="3">
         <v>66200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>70800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>64500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>97500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>49200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2590,35 +2732,38 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E62" s="3">
         <v>42400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>10800</v>
       </c>
       <c r="J62" s="3">
         <v>10800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>10800</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,48 +2900,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181400</v>
+      </c>
+      <c r="E66" s="3">
         <v>183700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>201200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>148400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>165100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>116600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,38 +3128,41 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-45300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-153100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-171000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-130200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-200</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,38 +3296,41 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>278700</v>
+      </c>
+      <c r="E76" s="3">
         <v>265700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>242000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>146100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>55600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>298000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>300100</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>0</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,82 +3380,88 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E81" s="3">
         <v>15500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>94900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-64800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="L81" s="3">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,29 +3490,30 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10700</v>
+        <v>15400</v>
       </c>
       <c r="E83" s="3">
         <v>10700</v>
       </c>
       <c r="F83" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G83" s="3">
         <v>8200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,38 +3739,41 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E89" s="3">
         <v>24900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>62000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-33500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-60700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-600</v>
       </c>
       <c r="J89" s="3">
         <v>-600</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,29 +3802,30 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,36 +3925,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-310000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,48 +4153,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>78700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>81600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>311500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3989,46 +4237,52 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>ORGO</t>
   </si>
@@ -730,7 +730,7 @@
         <v>450900</v>
       </c>
       <c r="F8" s="3">
-        <v>468100</v>
+        <v>467400</v>
       </c>
       <c r="G8" s="3">
         <v>338300</v>
@@ -742,7 +742,7 @@
         <v>193400</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>198500</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -783,8 +783,8 @@
       <c r="I9" s="3">
         <v>68800</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>61200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -814,7 +814,7 @@
         <v>345900</v>
       </c>
       <c r="F10" s="3">
-        <v>353900</v>
+        <v>353200</v>
       </c>
       <c r="G10" s="3">
         <v>251000</v>
@@ -825,8 +825,8 @@
       <c r="I10" s="3">
         <v>124600</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>137300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -885,8 +885,8 @@
       <c r="I12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="J12" s="3">
+        <v>9100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -952,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F14" s="3">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="G14" s="3">
-        <v>-2200</v>
+        <v>-1400</v>
       </c>
       <c r="H14" s="3">
         <v>1900</v>
       </c>
       <c r="I14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>9300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>420600</v>
+        <v>416800</v>
       </c>
       <c r="E17" s="3">
-        <v>428600</v>
+        <v>426300</v>
       </c>
       <c r="F17" s="3">
-        <v>397000</v>
+        <v>394400</v>
       </c>
       <c r="G17" s="3">
-        <v>309400</v>
+        <v>310800</v>
       </c>
       <c r="H17" s="3">
-        <v>292700</v>
+        <v>290800</v>
       </c>
       <c r="I17" s="3">
-        <v>247100</v>
+        <v>237900</v>
       </c>
       <c r="J17" s="3">
-        <v>4600</v>
+        <v>204200</v>
       </c>
       <c r="K17" s="3">
         <v>200</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12500</v>
+        <v>16300</v>
       </c>
       <c r="E18" s="3">
-        <v>22300</v>
+        <v>24600</v>
       </c>
       <c r="F18" s="3">
-        <v>71000</v>
+        <v>72900</v>
       </c>
       <c r="G18" s="3">
-        <v>28900</v>
+        <v>27500</v>
       </c>
       <c r="H18" s="3">
-        <v>-31700</v>
+        <v>-29900</v>
       </c>
       <c r="I18" s="3">
-        <v>-53700</v>
+        <v>-44400</v>
       </c>
       <c r="J18" s="3">
-        <v>-4600</v>
+        <v>-5700</v>
       </c>
       <c r="K18" s="3">
         <v>-200</v>
@@ -1153,7 +1153,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1162,16 +1162,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>2200</v>
+        <v>-2200</v>
       </c>
       <c r="I20" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>27900</v>
+        <v>31700</v>
       </c>
       <c r="E21" s="3">
-        <v>33000</v>
+        <v>35300</v>
       </c>
       <c r="F21" s="3">
-        <v>81800</v>
+        <v>83700</v>
       </c>
       <c r="G21" s="3">
-        <v>37200</v>
+        <v>35800</v>
       </c>
       <c r="H21" s="3">
-        <v>-20100</v>
+        <v>-17900</v>
       </c>
       <c r="I21" s="3">
-        <v>-46900</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-37700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1252,10 +1252,10 @@
         <v>9000</v>
       </c>
       <c r="I22" s="3">
-        <v>10900</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>10800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>8000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1285,7 +1285,7 @@
         <v>20300</v>
       </c>
       <c r="F23" s="3">
-        <v>63800</v>
+        <v>63100</v>
       </c>
       <c r="G23" s="3">
         <v>17800</v>
@@ -1297,7 +1297,7 @@
         <v>-64700</v>
       </c>
       <c r="J23" s="3">
-        <v>-2100</v>
+        <v>-14600</v>
       </c>
       <c r="K23" s="3">
         <v>-200</v>
@@ -1338,8 +1338,8 @@
       <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>-7000</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1411,7 +1411,7 @@
         <v>15500</v>
       </c>
       <c r="F26" s="3">
-        <v>94900</v>
+        <v>94200</v>
       </c>
       <c r="G26" s="3">
         <v>17200</v>
@@ -1423,7 +1423,7 @@
         <v>-64800</v>
       </c>
       <c r="J26" s="3">
-        <v>-2100</v>
+        <v>-7500</v>
       </c>
       <c r="K26" s="3">
         <v>-200</v>
@@ -1447,13 +1447,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E27" s="3">
         <v>15500</v>
       </c>
       <c r="F27" s="3">
-        <v>94900</v>
+        <v>94200</v>
       </c>
       <c r="G27" s="3">
         <v>17200</v>
@@ -1465,7 +1465,7 @@
         <v>-64800</v>
       </c>
       <c r="J27" s="3">
-        <v>-4400</v>
+        <v>-8800</v>
       </c>
       <c r="K27" s="3">
         <v>-200</v>
@@ -1657,7 +1657,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1666,16 +1666,16 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2200</v>
+        <v>2200</v>
       </c>
       <c r="I32" s="3">
-        <v>200</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
-        <v>-2500</v>
+        <v>-1000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         <v>15500</v>
       </c>
       <c r="F33" s="3">
-        <v>94900</v>
+        <v>94200</v>
       </c>
       <c r="G33" s="3">
         <v>17200</v>
       </c>
       <c r="H33" s="3">
-        <v>-39300</v>
+        <v>-38700</v>
       </c>
       <c r="I33" s="3">
         <v>-64800</v>
       </c>
       <c r="J33" s="3">
-        <v>-4400</v>
+        <v>-8400</v>
       </c>
       <c r="K33" s="3">
         <v>-200</v>
@@ -1789,19 +1789,19 @@
         <v>15500</v>
       </c>
       <c r="F35" s="3">
-        <v>94900</v>
+        <v>94200</v>
       </c>
       <c r="G35" s="3">
         <v>17200</v>
       </c>
       <c r="H35" s="3">
-        <v>-39300</v>
+        <v>-38700</v>
       </c>
       <c r="I35" s="3">
         <v>-64800</v>
       </c>
       <c r="J35" s="3">
-        <v>-4400</v>
+        <v>-8400</v>
       </c>
       <c r="K35" s="3">
         <v>-200</v>
@@ -1926,7 +1926,7 @@
         <v>21300</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>2300</v>
       </c>
       <c r="K41" s="3">
         <v>1000</v>
@@ -2009,8 +2009,8 @@
       <c r="I43" s="3">
         <v>34100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>28100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2049,10 +2049,10 @@
         <v>22900</v>
       </c>
       <c r="I44" s="3">
-        <v>13300</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>13400</v>
+      </c>
+      <c r="J44" s="3">
+        <v>14300</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11000</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
-        <v>5900</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>5600</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="3">
-        <v>5300</v>
+        <v>2600</v>
       </c>
       <c r="H45" s="3">
-        <v>3100</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="J45" s="3">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -2136,7 +2136,7 @@
         <v>71100</v>
       </c>
       <c r="J46" s="3">
-        <v>300</v>
+        <v>49700</v>
       </c>
       <c r="K46" s="3">
         <v>1400</v>
@@ -2168,14 +2168,14 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>600</v>
-      </c>
-      <c r="I47" s="3">
-        <v>500</v>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -2211,7 +2211,7 @@
         <v>128300</v>
       </c>
       <c r="G48" s="3">
-        <v>60100</v>
+        <v>55800</v>
       </c>
       <c r="H48" s="3">
         <v>47200</v>
@@ -2219,8 +2219,8 @@
       <c r="I48" s="3">
         <v>39600</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>42100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2261,8 +2261,8 @@
       <c r="I49" s="3">
         <v>51600</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>55300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>34000</v>
+        <v>6000</v>
       </c>
       <c r="E52" s="3">
-        <v>31500</v>
+        <v>1500</v>
       </c>
       <c r="F52" s="3">
-        <v>33500</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
       </c>
       <c r="H52" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J52" s="3">
-        <v>312500</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>310000</v>
@@ -2463,7 +2463,7 @@
         <v>443300</v>
       </c>
       <c r="G54" s="3">
-        <v>294500</v>
+        <v>290200</v>
       </c>
       <c r="H54" s="3">
         <v>220700</v>
@@ -2472,7 +2472,7 @@
         <v>163700</v>
       </c>
       <c r="J54" s="3">
-        <v>312800</v>
+        <v>148700</v>
       </c>
       <c r="K54" s="3">
         <v>311400</v>
@@ -2549,8 +2549,8 @@
       <c r="I57" s="3">
         <v>19200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>19100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2574,13 +2574,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6600</v>
+        <v>22000</v>
       </c>
       <c r="E58" s="3">
-        <v>4500</v>
+        <v>18700</v>
       </c>
       <c r="F58" s="3">
-        <v>2900</v>
+        <v>18600</v>
       </c>
       <c r="G58" s="3">
         <v>20300</v>
@@ -2589,10 +2589,10 @@
         <v>3100</v>
       </c>
       <c r="I58" s="3">
-        <v>10000</v>
+        <v>4800</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>5400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>43200</v>
+        <v>6400</v>
       </c>
       <c r="E59" s="3">
-        <v>38200</v>
+        <v>3600</v>
       </c>
       <c r="F59" s="3">
-        <v>49800</v>
+        <v>4400</v>
       </c>
       <c r="G59" s="3">
-        <v>24600</v>
+        <v>2600</v>
       </c>
       <c r="H59" s="3">
-        <v>28400</v>
+        <v>7900</v>
       </c>
       <c r="I59" s="3">
-        <v>37200</v>
+        <v>16900</v>
       </c>
       <c r="J59" s="3">
-        <v>3800</v>
+        <v>7300</v>
       </c>
       <c r="K59" s="3">
         <v>500</v>
@@ -2664,7 +2664,7 @@
         <v>75000</v>
       </c>
       <c r="F60" s="3">
-        <v>82000</v>
+        <v>82700</v>
       </c>
       <c r="G60" s="3">
         <v>68200</v>
@@ -2673,10 +2673,10 @@
         <v>59900</v>
       </c>
       <c r="I60" s="3">
-        <v>66400</v>
+        <v>56100</v>
       </c>
       <c r="J60" s="3">
-        <v>3900</v>
+        <v>52000</v>
       </c>
       <c r="K60" s="3">
         <v>500</v>
@@ -2700,13 +2700,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>62600</v>
+        <v>99600</v>
       </c>
       <c r="E61" s="3">
-        <v>66200</v>
+        <v>107500</v>
       </c>
       <c r="F61" s="3">
-        <v>70800</v>
+        <v>117700</v>
       </c>
       <c r="G61" s="3">
         <v>64500</v>
@@ -2715,10 +2715,10 @@
         <v>97500</v>
       </c>
       <c r="I61" s="3">
-        <v>49200</v>
+        <v>54500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>101500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>38200</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>42400</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>48500</v>
+        <v>1600</v>
       </c>
       <c r="G62" s="3">
         <v>15700</v>
@@ -2757,10 +2757,10 @@
         <v>7700</v>
       </c>
       <c r="I62" s="3">
-        <v>1000</v>
+        <v>6100</v>
       </c>
       <c r="J62" s="3">
-        <v>10800</v>
+        <v>10600</v>
       </c>
       <c r="K62" s="3">
         <v>10800</v>
@@ -2916,7 +2916,7 @@
         <v>183700</v>
       </c>
       <c r="F66" s="3">
-        <v>201200</v>
+        <v>201900</v>
       </c>
       <c r="G66" s="3">
         <v>148400</v>
@@ -2928,7 +2928,7 @@
         <v>116600</v>
       </c>
       <c r="J66" s="3">
-        <v>14800</v>
+        <v>164000</v>
       </c>
       <c r="K66" s="3">
         <v>11300</v>
@@ -3144,10 +3144,10 @@
         <v>-45300</v>
       </c>
       <c r="F72" s="3">
-        <v>-60100</v>
+        <v>-60800</v>
       </c>
       <c r="G72" s="3">
-        <v>-153100</v>
+        <v>-155000</v>
       </c>
       <c r="H72" s="3">
         <v>-171000</v>
@@ -3156,7 +3156,7 @@
         <v>-130200</v>
       </c>
       <c r="J72" s="3">
-        <v>-2300</v>
+        <v>-65400</v>
       </c>
       <c r="K72" s="3">
         <v>-200</v>
@@ -3312,10 +3312,10 @@
         <v>265700</v>
       </c>
       <c r="F76" s="3">
-        <v>242000</v>
+        <v>241300</v>
       </c>
       <c r="G76" s="3">
-        <v>146100</v>
+        <v>141800</v>
       </c>
       <c r="H76" s="3">
         <v>55600</v>
@@ -3324,7 +3324,7 @@
         <v>47000</v>
       </c>
       <c r="J76" s="3">
-        <v>298000</v>
+        <v>-15300</v>
       </c>
       <c r="K76" s="3">
         <v>300100</v>
@@ -3443,19 +3443,19 @@
         <v>15500</v>
       </c>
       <c r="F81" s="3">
-        <v>94900</v>
+        <v>94200</v>
       </c>
       <c r="G81" s="3">
         <v>17200</v>
       </c>
       <c r="H81" s="3">
-        <v>-39300</v>
+        <v>-38700</v>
       </c>
       <c r="I81" s="3">
         <v>-64800</v>
       </c>
       <c r="J81" s="3">
-        <v>-4400</v>
+        <v>-8400</v>
       </c>
       <c r="K81" s="3">
         <v>-200</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="E83" s="3">
-        <v>10700</v>
+        <v>13100</v>
       </c>
       <c r="F83" s="3">
-        <v>10700</v>
+        <v>11700</v>
       </c>
       <c r="G83" s="3">
-        <v>8200</v>
+        <v>4400</v>
       </c>
       <c r="H83" s="3">
-        <v>9400</v>
+        <v>3800</v>
       </c>
       <c r="I83" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>3300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3764,10 +3764,10 @@
         <v>-33500</v>
       </c>
       <c r="I89" s="3">
-        <v>-60700</v>
+        <v>-60600</v>
       </c>
       <c r="J89" s="3">
-        <v>-600</v>
+        <v>-3500</v>
       </c>
       <c r="K89" s="3">
         <v>-600</v>
@@ -3826,8 +3826,8 @@
       <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>-2400</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3953,7 +3953,7 @@
         <v>-1900</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-14900</v>
       </c>
       <c r="K94" s="3">
         <v>-310000</v>
@@ -4178,10 +4178,10 @@
         <v>78700</v>
       </c>
       <c r="I100" s="3">
-        <v>81600</v>
+        <v>81500</v>
       </c>
       <c r="J100" s="3">
-        <v>-300</v>
+        <v>18900</v>
       </c>
       <c r="K100" s="3">
         <v>311500</v>
@@ -4204,26 +4204,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>19000</v>
       </c>
       <c r="J102" s="3">
-        <v>-900</v>
+        <v>500</v>
       </c>
       <c r="K102" s="3">
         <v>900</v>

--- a/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>ORGO</t>
   </si>
@@ -656,102 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E8" s="3">
         <v>433100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>450900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>467400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>338300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>261000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>193400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>198500</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
+      <c r="M8" s="3">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
@@ -759,36 +762,39 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E9" s="3">
         <v>106500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>105000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>114200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>87300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>75900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>68800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,36 +807,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>366300</v>
+      </c>
+      <c r="E10" s="3">
         <v>326700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>345900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>353200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>251000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>185000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>124600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>137300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,35 +874,36 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E12" s="3">
         <v>44400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,36 +961,39 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E14" s="3">
         <v>3800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,36 +1006,39 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E15" s="3">
         <v>15400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>10700</v>
       </c>
       <c r="F15" s="3">
         <v>10700</v>
       </c>
       <c r="G15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H15" s="3">
         <v>8200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,40 +1070,41 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E17" s="3">
         <v>416800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>426300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>394400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>310800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>290800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>237900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>204200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
@@ -1086,41 +1112,44 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E18" s="3">
         <v>16300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>72900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,40 +1179,41 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1188,36 +1221,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E21" s="3">
         <v>31700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>35300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>83700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>35800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,36 +1266,39 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,41 +1311,44 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>10400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>63100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-64700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1314,41 +1356,44 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-31100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7000</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,41 +1446,44 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>94200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-64800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1440,41 +1491,44 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>94200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-39300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-64800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,41 +1716,44 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1692,41 +1761,44 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>94200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-64800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,41 +1851,44 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>94200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-64800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -1818,56 +1896,62 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,58 +1987,62 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135600</v>
+      </c>
+      <c r="E41" s="3">
         <v>103800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>102500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>113900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1985,36 +2074,39 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E43" s="3">
         <v>82000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>89500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,36 +2119,39 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E44" s="3">
         <v>28300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
       </c>
       <c r="J45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,51 +2209,57 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>285900</v>
+      </c>
+      <c r="E46" s="3">
         <v>225000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>222600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>227000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>174300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>125600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>71100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2195,36 +2299,39 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E48" s="3">
         <v>156300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>145700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>128300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>47200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,36 +2344,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E49" s="3">
         <v>44600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>49600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>54400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>59400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>51600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>55300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>310000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>497900</v>
+      </c>
+      <c r="E54" s="3">
         <v>460000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>449400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>443300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>290200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>220700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>163700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>148700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>311400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2655,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E57" s="3">
         <v>30700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,162 +2697,174 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E58" s="3">
         <v>22000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>6400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E60" s="3">
         <v>80500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>68200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E61" s="3">
         <v>99600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>107500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>117700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>64500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>97500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>101500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,39 +2877,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E66" s="3">
         <v>181400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>183700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>201900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>148400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>165100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>116600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>164000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,14 +3211,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>122400</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,41 +3301,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-155000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-171000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-130200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-200</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,41 +3481,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E76" s="3">
         <v>278700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>265700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>241300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>141800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>55600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300100</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>0</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,88 +3571,94 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>94200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-64800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18500</v>
+        <v>13600</v>
       </c>
       <c r="E83" s="3">
-        <v>13100</v>
+        <v>10400</v>
       </c>
       <c r="F83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="G83" s="3">
         <v>11700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,41 +3955,44 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E89" s="3">
         <v>30900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>62000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-33500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-60600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-310000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>42500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>78700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>81500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>311500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,8 +4473,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>ORGO</t>
   </si>
@@ -656,108 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>564200</v>
+      </c>
+      <c r="E8" s="3">
         <v>482000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>433100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>450900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>467400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>338300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>261000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>193400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>198500</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
+      <c r="N8" s="3">
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
@@ -765,39 +768,42 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>137500</v>
+      </c>
+      <c r="E9" s="3">
         <v>115700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>106500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>105000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>114200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>87300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>75900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>68800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,39 +816,42 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>426600</v>
+      </c>
+      <c r="E10" s="3">
         <v>366300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>326700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>345900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>353200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>251000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>185000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>124600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>137300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,38 +887,39 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E12" s="3">
         <v>50300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>44400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>39800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,39 +980,42 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E14" s="3">
         <v>22800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,39 +1028,42 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E15" s="3">
         <v>17000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>10700</v>
       </c>
       <c r="G15" s="3">
         <v>10700</v>
       </c>
       <c r="H15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I15" s="3">
         <v>8200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,43 +1096,44 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>507800</v>
+      </c>
+      <c r="E17" s="3">
         <v>460500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>416800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>426300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>394400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>310800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>290800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>237900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>204200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
@@ -1115,44 +1141,47 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E18" s="3">
         <v>21500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>72900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-44400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,8 +1212,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1189,34 +1222,34 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1224,39 +1257,42 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E21" s="3">
         <v>38600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>31700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>83700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,39 +1305,42 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,44 +1353,47 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>63100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-64700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1359,44 +1401,47 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-31100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,44 +1497,47 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E26" s="3">
         <v>900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>94200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-64800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1494,44 +1545,47 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>94200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-64800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,9 +1785,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1729,34 +1798,34 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1764,44 +1833,47 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>94200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-64800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,44 +1929,47 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>94200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-64800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -1899,59 +1977,65 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,65 +2073,69 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E41" s="3">
         <v>135600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>103800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>102500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>113900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>60200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E42" s="3">
         <v>300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2077,39 +2166,42 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E43" s="3">
         <v>109900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>89500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>82500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,39 +2214,42 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E44" s="3">
         <v>26200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>22900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>5500</v>
       </c>
       <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1000</v>
       </c>
       <c r="J45" s="3">
         <v>1000</v>
       </c>
       <c r="K45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,54 +2310,60 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>362200</v>
+      </c>
+      <c r="E46" s="3">
         <v>285900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>225000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>222600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>227000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>174300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>125600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>71100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2302,39 +2406,42 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>159500</v>
+      </c>
+      <c r="E48" s="3">
         <v>126200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>156300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>145700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>128300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,39 +2454,42 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E49" s="3">
         <v>41200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>44600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>49600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>54400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>51600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>55300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3800</v>
+        <v>9200</v>
       </c>
       <c r="E52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>310000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>598700</v>
+      </c>
+      <c r="E54" s="3">
         <v>497900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>460000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>449400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>443300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>290200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>220700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>163700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>148700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>311400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,38 +2785,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E57" s="3">
         <v>28900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,174 +2830,186 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E58" s="3">
         <v>9100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100100</v>
+      </c>
+      <c r="E60" s="3">
         <v>77500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>68200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>59900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E61" s="3">
         <v>34200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>99600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>107500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>117700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>64500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>97500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>101500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,42 +3022,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E66" s="3">
         <v>112600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>181400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>183700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>201900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>148400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>165100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>116600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,18 +3378,21 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E70" s="3">
         <v>122400</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,44 +3474,47 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-40100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-155000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-171000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-130200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-65400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-200</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,44 +3666,47 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>300100</v>
+      </c>
+      <c r="E76" s="3">
         <v>262900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>278700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>265700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>241300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>141800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>55600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-15300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>300100</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,94 +3762,100 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>94200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-64800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,38 +3886,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E83" s="3">
         <v>13600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,44 +4171,47 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>14200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-33500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-60600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,38 +4242,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-33900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-33900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-310000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E100" s="3">
         <v>27600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>42500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>78700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>81500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>311500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4476,8 +4724,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E102" s="3">
         <v>31800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORGO_YR_FIN.xlsx
@@ -778,7 +778,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>137500</v>
+        <v>132300</v>
       </c>
       <c r="E9" s="3">
         <v>115700</v>
@@ -826,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>426600</v>
+        <v>431800</v>
       </c>
       <c r="E10" s="3">
         <v>366300</v>
@@ -990,7 +990,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>11700</v>
+        <v>16900</v>
       </c>
       <c r="E14" s="3">
         <v>22800</v>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>507800</v>
+        <v>502600</v>
       </c>
       <c r="E17" s="3">
         <v>460500</v>
@@ -1151,7 +1151,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>56400</v>
+        <v>61600</v>
       </c>
       <c r="E18" s="3">
         <v>21500</v>
@@ -1267,7 +1267,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>75000</v>
+        <v>80200</v>
       </c>
       <c r="E21" s="3">
         <v>38600</v>
